--- a/mesures.xlsx
+++ b/mesures.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idris\Documents\GitHub\Ratiananahary-Mekidiche-Lepape-mesures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\GitHub\Ratiananahary-Mekidiche-Lepape-mesures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C3F296-1887-4480-ACF8-F49BC9B23052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0586DDBC-3A58-4236-9AEF-5F419A31DF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{89837A86-A6A0-43CB-8C11-52B8E1DB3969}"/>
+    <workbookView xWindow="7515" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{89837A86-A6A0-43CB-8C11-52B8E1DB3969}"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
+    <sheet name="CC" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Total lignes</t>
   </si>
@@ -58,15 +58,54 @@
   </si>
   <si>
     <t>Lignes blanches</t>
+  </si>
+  <si>
+    <t>Complexité Cyclomatique</t>
+  </si>
+  <si>
+    <t>Éléments</t>
+  </si>
+  <si>
+    <t>Nombre de nœuds (N)</t>
+  </si>
+  <si>
+    <t>Nombre d'arêtes ( E )</t>
+  </si>
+  <si>
+    <t>Nombre de prédicats (P)</t>
+  </si>
+  <si>
+    <t>CC avec E - N + 2</t>
+  </si>
+  <si>
+    <t>CC avec P + 1</t>
+  </si>
+  <si>
+    <t>Valeur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -93,8 +132,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,16 +471,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07F3B09-67F9-4B89-9E3D-9D42149FBDB7}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.53125" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.796875" customWidth="1"/>
+    <col min="4" max="4" width="19.86328125" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -456,7 +497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -480,9 +521,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEB3EEB-BFF8-48C4-A50A-2FC0998C3599}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="26.1328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.6">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <f>B5-B4+2</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <f>B6+1</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mesures.xlsx
+++ b/mesures.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documents\GitHub\Ratiananahary-Mekidiche-Lepape-mesures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\idris\Documents\GitHub\Ratiananahary-Mekidiche-Lepape-mesures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0586DDBC-3A58-4236-9AEF-5F419A31DF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9D85FC-AC6A-4F14-A98C-0AAE4E534826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7515" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{89837A86-A6A0-43CB-8C11-52B8E1DB3969}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{89837A86-A6A0-43CB-8C11-52B8E1DB3969}"/>
   </bookViews>
   <sheets>
     <sheet name="LOC" sheetId="1" r:id="rId1"/>
     <sheet name="CC" sheetId="2" r:id="rId2"/>
+    <sheet name="HALSTEAD" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="92">
   <si>
     <t>Total lignes</t>
   </si>
@@ -82,13 +84,250 @@
   </si>
   <si>
     <t>Valeur</t>
+  </si>
+  <si>
+    <t>Mesure</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>++</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Nt</t>
+  </si>
+  <si>
+    <t>TOTAL occurrences</t>
+  </si>
+  <si>
+    <t>nt</t>
+  </si>
+  <si>
+    <t>TOTAL distincts</t>
+  </si>
+  <si>
+    <t>Opérateur</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t>[</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>return</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t>(</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>void</t>
+  </si>
+  <si>
+    <t>Occurrences</t>
+  </si>
+  <si>
+    <t>Nd</t>
+  </si>
+  <si>
+    <t>nd</t>
+  </si>
+  <si>
+    <t>swap — appels</t>
+  </si>
+  <si>
+    <t>iqsort — appels</t>
+  </si>
+  <si>
+    <t>iqsort — définition</t>
+  </si>
+  <si>
+    <t>0 — argument de swap</t>
+  </si>
+  <si>
+    <t>0 — condition/initialisation</t>
+  </si>
+  <si>
+    <t>1 — expression arithmétique</t>
+  </si>
+  <si>
+    <t>1 — condition/initialisation</t>
+  </si>
+  <si>
+    <t>j — argument/expression</t>
+  </si>
+  <si>
+    <t>j — incrément ++j</t>
+  </si>
+  <si>
+    <t>j — déclaration/initialisation</t>
+  </si>
+  <si>
+    <t>i — index/argument</t>
+  </si>
+  <si>
+    <t>i — boucle for</t>
+  </si>
+  <si>
+    <t>i — déclaration</t>
+  </si>
+  <si>
+    <t>n-j-1 — expression arithmétique</t>
+  </si>
+  <si>
+    <t>n — utilisation simple</t>
+  </si>
+  <si>
+    <t>a+j+1 — expression arithmétique</t>
+  </si>
+  <si>
+    <t>a[i] — base/indexation</t>
+  </si>
+  <si>
+    <t>a — utilisation simple</t>
+  </si>
+  <si>
+    <t>Opérande / contexte</t>
+  </si>
+  <si>
+    <t>Symbole</t>
+  </si>
+  <si>
+    <t>Résultat</t>
+  </si>
+  <si>
+    <t>Formule</t>
+  </si>
+  <si>
+    <t>Opérateurs distincts</t>
+  </si>
+  <si>
+    <t>Comptage des opérateurs distincts</t>
+  </si>
+  <si>
+    <t>Occurrences totales d'opérateurs</t>
+  </si>
+  <si>
+    <t>Somme des occurrences d'opérateurs</t>
+  </si>
+  <si>
+    <t>Opérandes distincts</t>
+  </si>
+  <si>
+    <t>Comptage des opérandes distincts selon la convention retenue</t>
+  </si>
+  <si>
+    <t>Occurrences totales d'opérandes</t>
+  </si>
+  <si>
+    <t>Somme des occurrences d'opérandes</t>
+  </si>
+  <si>
+    <t>Vocabulaire</t>
+  </si>
+  <si>
+    <t>nt + nd</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Longueur</t>
+  </si>
+  <si>
+    <t>Nt + Nd</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>N × log2(n)</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Difficulté</t>
+  </si>
+  <si>
+    <t>(nt / 2) × (Nd / nd)</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>D × V</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>I</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,16 +350,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -128,14 +378,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,16 +740,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07F3B09-67F9-4B89-9E3D-9D42149FBDB7}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.53125" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" customWidth="1"/>
-    <col min="4" max="4" width="19.86328125" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -497,7 +766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -522,17 +791,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEB3EEB-BFF8-48C4-A50A-2FC0998C3599}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.1328125" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -540,7 +809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -548,7 +817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -556,7 +825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -564,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -573,7 +842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -586,4 +855,492 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{691183A6-BBBC-484D-8B27-6EC3F5FB7D08}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="53.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="5">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="5">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="5">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="3">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="6">
+        <v>25</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="6">
+        <f>SUM(G5+G3)</f>
+        <v>84</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="6">
+        <f>G7*LOG(G6,2)</f>
+        <v>390.08391994107683</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="6">
+        <f>(G2/2)*(G5/G4)</f>
+        <v>38.25</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="6">
+        <f>G8*G9</f>
+        <v>14920.709937746189</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <f>COUNTA(C2:C19)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <f>SUM(D2:D19)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <f>COUNTA(A2:A21)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <f>SUM(B2:B21)</f>
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69ED2A8A-1F91-47FD-8139-1D62D1602299}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>